--- a/测试git.xlsx
+++ b/测试git.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\16278\Documents\钢厂业务\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\16278\daiyangit\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>来源</t>
   </si>
@@ -287,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,12 +297,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,12 +304,6 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.4"/>
         <bgColor rgb="FF2F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
-        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -680,7 +668,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -704,16 +692,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="9">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
@@ -722,115 +710,112 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1143,8 +1128,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
+  <cols>
+    <col min="4" max="4" width="24.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="29.4545454545455" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
       <c r="A1" s="3" t="s">
@@ -1188,11 +1177,11 @@
       <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="145" spans="1:7">
+    <row r="3" s="2" customFormat="1" ht="130.5" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1211,7 +1200,30 @@
       <c r="F3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="130.5" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>13</v>
       </c>
     </row>

--- a/测试git.xlsx
+++ b/测试git.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>来源</t>
   </si>
@@ -1128,8 +1128,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="24.7272727272727" customWidth="1"/>
     <col min="6" max="6" width="29.4545454545455" customWidth="1"/>
@@ -1158,7 +1158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="188.5" spans="1:7">
+    <row r="2" s="2" customFormat="1" ht="101.5" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -1224,6 +1224,29 @@
         <v>16</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="130.5" spans="1:7">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>13</v>
       </c>
     </row>

--- a/测试git.xlsx
+++ b/测试git.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="17">
   <si>
     <t>来源</t>
   </si>
@@ -287,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,6 +297,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,7 +674,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -692,16 +698,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
@@ -710,89 +716,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -802,10 +808,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -815,6 +824,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -870,6 +888,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FFFF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1128,125 +1151,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="24.7272727272727" customWidth="1"/>
     <col min="6" max="6" width="29.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="101.5" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="130.5" spans="1:7">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="130.5" spans="1:7">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="130.5" spans="1:7">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="130.5" spans="1:7">
+      <c r="A6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>13</v>
       </c>
     </row>

--- a/测试git.xlsx
+++ b/测试git.xlsx
@@ -1151,8 +1151,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="24.7272727272727" customWidth="1"/>
     <col min="6" max="6" width="29.4545454545455" customWidth="1"/>
@@ -1294,6 +1294,11 @@
       </c>
       <c r="G6" s="10" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
